--- a/JsonConverter/ExcelFiles/UI.xlsx
+++ b/JsonConverter/ExcelFiles/UI.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="13272" windowHeight="5856"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="33">
   <si>
     <t>아이디</t>
   </si>
@@ -41,9 +41,6 @@
     <t>게임 상태 바인딩</t>
   </si>
   <si>
-    <t>프리팹 경로</t>
-  </si>
-  <si>
     <t>string</t>
   </si>
   <si>
@@ -65,9 +62,6 @@
     <t>BindState</t>
   </si>
   <si>
-    <t>PrefabPath</t>
-  </si>
-  <si>
     <t>UI_Popup_01</t>
   </si>
   <si>
@@ -77,36 +71,24 @@
     <t>Popup</t>
   </si>
   <si>
-    <t>Prefabs/UI/Popup/OpenedStage</t>
-  </si>
-  <si>
     <t>UI_Popup_02</t>
   </si>
   <si>
     <t>ClosedStage</t>
   </si>
   <si>
-    <t>Prefabs/UI/Popup/ClosedStage</t>
-  </si>
-  <si>
     <t>UI_Popup_03</t>
   </si>
   <si>
     <t>StageClear</t>
   </si>
   <si>
-    <t>Prefabs/UI/Popup/StageClear</t>
-  </si>
-  <si>
     <t>UI_Popup_04</t>
   </si>
   <si>
     <t>StageFailed</t>
   </si>
   <si>
-    <t>Prefabs/UI/Popup/StageFailed</t>
-  </si>
-  <si>
     <t>UI_Panel_01</t>
   </si>
   <si>
@@ -116,18 +98,12 @@
     <t>Main</t>
   </si>
   <si>
-    <t>Prefabs/UI/Panel/MainMenu</t>
-  </si>
-  <si>
     <t>UI_Panel_02</t>
   </si>
   <si>
     <t>GamePlay</t>
   </si>
   <si>
-    <t>Prefabs/UI/Panel/GamePlay</t>
-  </si>
-  <si>
     <t>UI_Panel_03</t>
   </si>
   <si>
@@ -137,18 +113,12 @@
     <t>Lobby</t>
   </si>
   <si>
-    <t>Prefabs/UI/Panel/GameLobby</t>
-  </si>
-  <si>
     <t>UI_Panel_04</t>
   </si>
   <si>
     <t>Upgrade</t>
   </si>
   <si>
-    <t>Prefabs/UI/Panel/Upgrade</t>
-  </si>
-  <si>
     <t>UI_Loading_01</t>
   </si>
   <si>
@@ -156,9 +126,6 @@
   </si>
   <si>
     <t>VeryFront</t>
-  </si>
-  <si>
-    <t>Prefabs/UI/Panel/Loading</t>
   </si>
 </sst>
 </file>
@@ -802,7 +769,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -825,9 +792,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1355,20 +1319,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H22"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="15.5555555555556" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="13.6666666666667" customWidth="1"/>
     <col min="4" max="4" width="16.5555555555556" customWidth="1"/>
-    <col min="5" max="5" width="33.5555555555556" customWidth="1"/>
-    <col min="6" max="6" width="14.4444444444444" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="32.2222222222222" customWidth="1"/>
+    <col min="5" max="5" width="14.4444444444444" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="32.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1381,273 +1344,227 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
+      <c r="E1" s="3"/>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-    </row>
-    <row r="2" spans="1:8">
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-    </row>
-    <row r="3" spans="1:8">
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-    </row>
-    <row r="4" spans="1:8">
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="D4" s="2"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2" t="s">
+      <c r="C5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1" t="s">
+      <c r="C7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="1" t="s">
+      <c r="D8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="6"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="1" t="s">
+      <c r="C9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" spans="1:7">
+      <c r="A10" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="1" t="s">
+      <c r="B10" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="2" t="s">
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="B11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="6"/>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="1" t="s">
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="C12" s="7" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="10" customFormat="1" spans="1:8">
-      <c r="A10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>42</v>
-      </c>
       <c r="D12" s="7"/>
-      <c r="E12" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-    </row>
-    <row r="14" spans="1:8">
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" s="1"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
-      <c r="E14" s="1"/>
-    </row>
-    <row r="15" spans="1:8">
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" s="1"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
-      <c r="E15" s="1"/>
-    </row>
-    <row r="16" spans="1:8">
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" s="1"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
-      <c r="E16" s="8"/>
-    </row>
-    <row r="17" spans="1:6">
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="1"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
-      <c r="E17" s="1"/>
-    </row>
-    <row r="18" spans="1:6">
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="6"/>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="E18" s="6"/>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-    </row>
-    <row r="20" spans="1:6">
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-    </row>
-    <row r="21" spans="1:6">
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-    </row>
-    <row r="22" spans="1:6">
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/JsonConverter/ExcelFiles/UI.xlsx
+++ b/JsonConverter/ExcelFiles/UI.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13272" windowHeight="5856"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="44">
   <si>
     <t>아이디</t>
   </si>
@@ -41,6 +41,9 @@
     <t>게임 상태 바인딩</t>
   </si>
   <si>
+    <t>상태 진입시 자동 스폰 여부</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
@@ -50,6 +53,9 @@
     <t>GameState</t>
   </si>
   <si>
+    <t>bool</t>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
@@ -62,6 +68,9 @@
     <t>BindState</t>
   </si>
   <si>
+    <t>AutoSpawn</t>
+  </si>
+  <si>
     <t>UI_Popup_01</t>
   </si>
   <si>
@@ -71,6 +80,12 @@
     <t>Popup</t>
   </si>
   <si>
+    <t>Lobby</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>UI_Popup_02</t>
   </si>
   <si>
@@ -83,12 +98,33 @@
     <t>StageClear</t>
   </si>
   <si>
+    <t>GamePlay</t>
+  </si>
+  <si>
     <t>UI_Popup_04</t>
   </si>
   <si>
     <t>StageFailed</t>
   </si>
   <si>
+    <t>UI_Popup_05</t>
+  </si>
+  <si>
+    <t>PlanetInfo</t>
+  </si>
+  <si>
+    <t>UI_Popup_06</t>
+  </si>
+  <si>
+    <t>RefinerUpgrade</t>
+  </si>
+  <si>
+    <t>UI_Popup_07</t>
+  </si>
+  <si>
+    <t>FarmUpgrade</t>
+  </si>
+  <si>
     <t>UI_Panel_01</t>
   </si>
   <si>
@@ -98,19 +134,16 @@
     <t>Main</t>
   </si>
   <si>
+    <t>true</t>
+  </si>
+  <si>
     <t>UI_Panel_02</t>
   </si>
   <si>
-    <t>GamePlay</t>
-  </si>
-  <si>
     <t>UI_Panel_03</t>
   </si>
   <si>
     <t>GameLobby</t>
-  </si>
-  <si>
-    <t>Lobby</t>
   </si>
   <si>
     <t>UI_Panel_04</t>
@@ -132,12 +165,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="0.0_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -769,26 +801,38 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -1319,252 +1363,372 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="15.5555555555556" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="13.6666666666667" customWidth="1"/>
     <col min="4" max="4" width="16.5555555555556" customWidth="1"/>
-    <col min="5" max="5" width="14.4444444444444" customWidth="1"/>
+    <col min="5" max="5" width="24.2222222222222" style="1" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="32.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5"/>
+      <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="6"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="A3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="B3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
+      <c r="C3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="6"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
+      <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="6"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="6"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="D6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="9"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="9"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="9"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="9"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="9"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="9"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="9"/>
+    </row>
+    <row r="13" customFormat="1" spans="1:7">
+      <c r="A13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="1" t="s">
+      <c r="E13" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" s="9"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="6"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" customFormat="1" spans="1:7">
-      <c r="A10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="7"/>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="1"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
+      <c r="F14" s="9"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="1"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
+      <c r="A15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" s="9"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="1"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="1"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="6"/>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="9"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="2"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="9"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="2"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="9"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="2"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="9"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="2"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="9"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="9"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="9"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="9"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="9"/>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/JsonConverter/ExcelFiles/UI.xlsx
+++ b/JsonConverter/ExcelFiles/UI.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="14136" windowHeight="8111"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="46">
   <si>
     <t>아이디</t>
   </si>
@@ -110,16 +110,22 @@
     <t>UI_Popup_05</t>
   </si>
   <si>
+    <t>StageStart</t>
+  </si>
+  <si>
+    <t>UI_Popup_06</t>
+  </si>
+  <si>
     <t>PlanetInfo</t>
   </si>
   <si>
-    <t>UI_Popup_06</t>
+    <t>UI_Popup_07</t>
   </si>
   <si>
     <t>RefinerUpgrade</t>
   </si>
   <si>
-    <t>UI_Popup_07</t>
+    <t>UI_Popup_08</t>
   </si>
   <si>
     <t>FarmUpgrade</t>
@@ -801,7 +807,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -817,9 +823,6 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -827,9 +830,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
@@ -1363,7 +1363,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="15.5555555555556" customWidth="1"/>
@@ -1391,8 +1391,8 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5"/>
-      <c r="G1" s="6"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
@@ -1410,27 +1410,27 @@
       <c r="E2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="6"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="6"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
@@ -1448,8 +1448,8 @@
       <c r="E4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="6"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2" t="s">
@@ -1467,8 +1467,8 @@
       <c r="E5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="6"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
@@ -1486,7 +1486,7 @@
       <c r="E6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="9"/>
+      <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2" t="s">
@@ -1504,7 +1504,7 @@
       <c r="E7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="9"/>
+      <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2" t="s">
@@ -1522,7 +1522,7 @@
       <c r="E8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="9"/>
+      <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2" t="s">
@@ -1540,7 +1540,7 @@
       <c r="E9" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="9"/>
+      <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2" t="s">
@@ -1558,7 +1558,7 @@
       <c r="E10" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="9"/>
+      <c r="F10" s="2"/>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2" t="s">
@@ -1568,69 +1568,69 @@
         <v>33</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" s="9"/>
+        <v>23</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="D12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" s="3" t="s">
+      <c r="C13" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="F12" s="9"/>
-    </row>
-    <row r="13" customFormat="1" spans="1:7">
-      <c r="A13" s="2" t="s">
+      <c r="E13" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="F13" s="9"/>
-    </row>
-    <row r="14" spans="1:7">
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" customFormat="1" spans="1:7">
       <c r="A14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="9" t="s">
         <v>40</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" s="9"/>
+      <c r="E14" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2" t="s">
@@ -1639,96 +1639,114 @@
       <c r="B15" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="F15" s="9"/>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="9"/>
+      <c r="B16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" s="2"/>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="9"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="2"/>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="2"/>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="2"/>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="2"/>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="2"/>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="9"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="2"/>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="9"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="2"/>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="9"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="2"/>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="9"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="2"/>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/JsonConverter/ExcelFiles/UI.xlsx
+++ b/JsonConverter/ExcelFiles/UI.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14136" windowHeight="8111"/>
+    <workbookView windowWidth="14568" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="44">
   <si>
     <t>아이디</t>
   </si>
@@ -122,13 +122,7 @@
     <t>UI_Popup_07</t>
   </si>
   <si>
-    <t>RefinerUpgrade</t>
-  </si>
-  <si>
-    <t>UI_Popup_08</t>
-  </si>
-  <si>
-    <t>FarmUpgrade</t>
+    <t>StationUpgrade</t>
   </si>
   <si>
     <t>UI_Panel_01</t>
@@ -1363,7 +1357,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="15.5555555555556" customWidth="1"/>
@@ -1568,67 +1562,67 @@
         <v>33</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>18</v>
+        <v>33</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="D12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="3" t="s">
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" customFormat="1" spans="1:7">
+      <c r="A13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>37</v>
-      </c>
       <c r="F13" s="2"/>
     </row>
-    <row r="14" customFormat="1" spans="1:7">
+    <row r="14" spans="1:7">
       <c r="A14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F14" s="2"/>
     </row>
@@ -1639,40 +1633,30 @@
       <c r="B15" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>17</v>
+      <c r="C15" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>42</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F15" s="2"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>37</v>
-      </c>
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="8"/>
       <c r="F16" s="2"/>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
       <c r="E17" s="8"/>
       <c r="F17" s="2"/>
     </row>
@@ -1702,9 +1686,9 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
       <c r="E21" s="8"/>
       <c r="F21" s="2"/>
     </row>
@@ -1740,14 +1724,6 @@
       <c r="E25" s="8"/>
       <c r="F25" s="2"/>
     </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="2"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/JsonConverter/ExcelFiles/UI.xlsx
+++ b/JsonConverter/ExcelFiles/UI.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14568" windowHeight="8400"/>
+    <workbookView windowWidth="13128" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="40">
   <si>
     <t>아이디</t>
   </si>
@@ -41,7 +41,7 @@
     <t>게임 상태 바인딩</t>
   </si>
   <si>
-    <t>상태 진입시 자동 스폰 여부</t>
+    <t>자동으로 열림 여부</t>
   </si>
   <si>
     <t>string</t>
@@ -68,82 +68,70 @@
     <t>BindState</t>
   </si>
   <si>
-    <t>AutoSpawn</t>
-  </si>
-  <si>
-    <t>UI_Popup_01</t>
-  </si>
-  <si>
-    <t>OpenedStage</t>
+    <t>Auto</t>
+  </si>
+  <si>
+    <t>UI_Popup_03</t>
+  </si>
+  <si>
+    <t>StageClear</t>
   </si>
   <si>
     <t>Popup</t>
   </si>
   <si>
+    <t>GamePlay</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>UI_Popup_04</t>
+  </si>
+  <si>
+    <t>StageFailed</t>
+  </si>
+  <si>
+    <t>UI_Popup_05</t>
+  </si>
+  <si>
+    <t>StageStart</t>
+  </si>
+  <si>
+    <t>UI_Popup_06</t>
+  </si>
+  <si>
+    <t>PlanetInfo</t>
+  </si>
+  <si>
+    <t>UI_Popup_07</t>
+  </si>
+  <si>
+    <t>StationUpgrade</t>
+  </si>
+  <si>
+    <t>UI_Panel_01</t>
+  </si>
+  <si>
+    <t>MainMenu</t>
+  </si>
+  <si>
+    <t>Main</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>UI_Panel_02</t>
+  </si>
+  <si>
+    <t>UI_Panel_03</t>
+  </si>
+  <si>
+    <t>GameLobby</t>
+  </si>
+  <si>
     <t>Lobby</t>
-  </si>
-  <si>
-    <t>false</t>
-  </si>
-  <si>
-    <t>UI_Popup_02</t>
-  </si>
-  <si>
-    <t>ClosedStage</t>
-  </si>
-  <si>
-    <t>UI_Popup_03</t>
-  </si>
-  <si>
-    <t>StageClear</t>
-  </si>
-  <si>
-    <t>GamePlay</t>
-  </si>
-  <si>
-    <t>UI_Popup_04</t>
-  </si>
-  <si>
-    <t>StageFailed</t>
-  </si>
-  <si>
-    <t>UI_Popup_05</t>
-  </si>
-  <si>
-    <t>StageStart</t>
-  </si>
-  <si>
-    <t>UI_Popup_06</t>
-  </si>
-  <si>
-    <t>PlanetInfo</t>
-  </si>
-  <si>
-    <t>UI_Popup_07</t>
-  </si>
-  <si>
-    <t>StationUpgrade</t>
-  </si>
-  <si>
-    <t>UI_Panel_01</t>
-  </si>
-  <si>
-    <t>MainMenu</t>
-  </si>
-  <si>
-    <t>Main</t>
-  </si>
-  <si>
-    <t>true</t>
-  </si>
-  <si>
-    <t>UI_Panel_02</t>
-  </si>
-  <si>
-    <t>UI_Panel_03</t>
-  </si>
-  <si>
-    <t>GameLobby</t>
   </si>
   <si>
     <t>UI_Panel_04</t>
@@ -1357,19 +1345,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="15.5555555555556" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="13.6666666666667" customWidth="1"/>
     <col min="4" max="4" width="16.5555555555556" customWidth="1"/>
-    <col min="5" max="5" width="24.2222222222222" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="32.2222222222222" customWidth="1"/>
+    <col min="5" max="5" width="20.2222222222222" style="1" customWidth="1"/>
+    <col min="6" max="6" width="32.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1385,10 +1372,9 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3"/>
-      <c r="G1" s="5"/>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="F1" s="5"/>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -1404,10 +1390,9 @@
       <c r="E2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="5"/>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="F2" s="5"/>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
@@ -1423,14 +1408,13 @@
       <c r="E3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="5"/>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="F3" s="5"/>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -1442,14 +1426,12 @@
       <c r="E4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="5"/>
-    </row>
-    <row r="5" spans="1:7">
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -1461,10 +1443,8 @@
       <c r="E5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="5"/>
-    </row>
-    <row r="6" spans="1:7">
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
         <v>21</v>
       </c>
@@ -1475,254 +1455,200 @@
         <v>16</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:7">
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:7">
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="1:7">
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="D9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="1:7">
+    </row>
+    <row r="11" customFormat="1" spans="1:6">
       <c r="A11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="9" t="s">
         <v>33</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="E11" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="2" t="s">
+      <c r="B12" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="C12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="E12" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" customFormat="1" spans="1:7">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>17</v>
+      <c r="C13" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F15" s="2"/>
-    </row>
-    <row r="16" spans="1:7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="8"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="2"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="8"/>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="2"/>
-    </row>
-    <row r="17" spans="1:6">
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="2"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="2"/>
-    </row>
-    <row r="18" spans="1:6">
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="2"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="2"/>
-    </row>
-    <row r="19" spans="1:6">
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="2"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
       <c r="E19" s="8"/>
-      <c r="F19" s="2"/>
-    </row>
-    <row r="20" spans="1:6">
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="2"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
       <c r="E20" s="8"/>
-      <c r="F20" s="2"/>
-    </row>
-    <row r="21" spans="1:6">
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="2"/>
-    </row>
-    <row r="22" spans="1:6">
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="2"/>
-    </row>
-    <row r="23" spans="1:6">
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="2"/>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="2"/>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/JsonConverter/ExcelFiles/UI.xlsx
+++ b/JsonConverter/ExcelFiles/UI.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13128" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="42">
   <si>
     <t>아이디</t>
   </si>
@@ -147,6 +147,12 @@
   </si>
   <si>
     <t>VeryFront</t>
+  </si>
+  <si>
+    <t>UI_Debug_01</t>
+  </si>
+  <si>
+    <t>DebugUI</t>
   </si>
 </sst>
 </file>
@@ -1581,11 +1587,21 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="8"/>
+      <c r="A14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2"/>

--- a/JsonConverter/ExcelFiles/UI.xlsx
+++ b/JsonConverter/ExcelFiles/UI.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="10968" windowHeight="5676"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="44">
   <si>
     <t>아이디</t>
   </si>
@@ -71,21 +71,30 @@
     <t>Auto</t>
   </si>
   <si>
+    <t>UI_Popup_02</t>
+  </si>
+  <si>
+    <t>ContinueInfo</t>
+  </si>
+  <si>
+    <t>Popup</t>
+  </si>
+  <si>
+    <t>MainMenu</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>UI_Popup_03</t>
   </si>
   <si>
     <t>StageClear</t>
   </si>
   <si>
-    <t>Popup</t>
-  </si>
-  <si>
     <t>GamePlay</t>
   </si>
   <si>
-    <t>false</t>
-  </si>
-  <si>
     <t>UI_Popup_04</t>
   </si>
   <si>
@@ -111,9 +120,6 @@
   </si>
   <si>
     <t>UI_Panel_01</t>
-  </si>
-  <si>
-    <t>MainMenu</t>
   </si>
   <si>
     <t>Main</t>
@@ -795,7 +801,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -818,6 +824,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
@@ -1351,7 +1363,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="15.5555555555556" customWidth="1"/>
@@ -1420,18 +1432,19 @@
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="9" t="s">
         <v>18</v>
       </c>
+      <c r="F4" s="5"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
@@ -1444,7 +1457,7 @@
         <v>16</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>18</v>
@@ -1452,16 +1465,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>18</v>
@@ -1469,16 +1482,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>18</v>
@@ -1486,16 +1499,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>18</v>
@@ -1503,70 +1516,70 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>30</v>
+        <v>21</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" customFormat="1" spans="1:6">
+      <c r="E10" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="3" t="s">
+    </row>
+    <row r="12" customFormat="1" spans="1:6">
+      <c r="A12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="2" t="s">
+      <c r="B12" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>18</v>
+      <c r="E12" s="10" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1576,95 +1589,112 @@
       <c r="B13" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>30</v>
+      <c r="C13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="2"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="8"/>
+      <c r="D15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="8"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="10"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="8"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="10"/>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="8"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="10"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="8"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
-      <c r="E20" s="8"/>
+      <c r="E20" s="10"/>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
-      <c r="E21" s="8"/>
+      <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
-      <c r="E22" s="8"/>
+      <c r="E22" s="10"/>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
-      <c r="E23" s="8"/>
+      <c r="E23" s="10"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/JsonConverter/ExcelFiles/UI.xlsx
+++ b/JsonConverter/ExcelFiles/UI.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="10968" windowHeight="5676"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
     <t>UI_Popup_02</t>
   </si>
   <si>
-    <t>ContinueInfo</t>
+    <t>SlotSelect</t>
   </si>
   <si>
     <t>Popup</t>

--- a/JsonConverter/ExcelFiles/UI.xlsx
+++ b/JsonConverter/ExcelFiles/UI.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="13776" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="46">
   <si>
     <t>아이디</t>
   </si>
@@ -71,19 +71,25 @@
     <t>Auto</t>
   </si>
   <si>
+    <t>UI_Popup_01</t>
+  </si>
+  <si>
+    <t>Confirm</t>
+  </si>
+  <si>
+    <t>Popup</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>UI_Popup_02</t>
   </si>
   <si>
     <t>SlotSelect</t>
   </si>
   <si>
-    <t>Popup</t>
-  </si>
-  <si>
     <t>MainMenu</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
   <si>
     <t>UI_Popup_03</t>
@@ -801,7 +807,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -824,6 +830,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
@@ -1363,7 +1375,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="15.5555555555556" customWidth="1"/>
@@ -1435,49 +1447,48 @@
       <c r="B4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="10"/>
+      <c r="E4" s="11" t="s">
         <v>17</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>18</v>
       </c>
       <c r="F4" s="5"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="E5" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="5"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1491,10 +1502,10 @@
         <v>16</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1508,10 +1519,10 @@
         <v>16</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1525,10 +1536,10 @@
         <v>16</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1536,67 +1547,67 @@
         <v>30</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" customFormat="1" spans="1:6">
+        <v>20</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="3" t="s">
+    </row>
+    <row r="13" customFormat="1" spans="1:6">
+      <c r="A13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E12" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="2" t="s">
+      <c r="B13" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>18</v>
+      <c r="E13" s="12" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1606,95 +1617,112 @@
       <c r="B14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>32</v>
+      <c r="C14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="2"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="10"/>
+      <c r="D16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="10"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="12"/>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="10"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="12"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="10"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="12"/>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="10"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="12"/>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
-      <c r="E21" s="10"/>
+      <c r="E21" s="12"/>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
-      <c r="E22" s="10"/>
+      <c r="E22" s="12"/>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
-      <c r="E23" s="10"/>
+      <c r="E23" s="12"/>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
-      <c r="E24" s="10"/>
+      <c r="E24" s="12"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/JsonConverter/ExcelFiles/UI.xlsx
+++ b/JsonConverter/ExcelFiles/UI.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13776" windowHeight="9660"/>
+    <workbookView windowWidth="13776" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="48">
   <si>
     <t>아이디</t>
   </si>
@@ -123,6 +123,12 @@
   </si>
   <si>
     <t>StationUpgrade</t>
+  </si>
+  <si>
+    <t>UI_Popup_08</t>
+  </si>
+  <si>
+    <t>StationMarket</t>
   </si>
   <si>
     <t>UI_Panel_01</t>
@@ -807,7 +813,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -833,9 +839,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
@@ -1375,7 +1378,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="15.5555555555556" customWidth="1"/>
@@ -1450,8 +1453,8 @@
       <c r="C4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="11" t="s">
+      <c r="D4" s="9"/>
+      <c r="E4" s="10" t="s">
         <v>17</v>
       </c>
       <c r="F4" s="5"/>
@@ -1469,7 +1472,7 @@
       <c r="D5" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="10" t="s">
         <v>17</v>
       </c>
       <c r="F5" s="5"/>
@@ -1564,67 +1567,67 @@
         <v>32</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>34</v>
+        <v>23</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="D12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" s="3" t="s">
+      <c r="C13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="12" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" customFormat="1" spans="1:6">
-      <c r="A13" s="2" t="s">
+      <c r="E13" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="3" t="s">
+    </row>
+    <row r="14" customFormat="1" spans="1:6">
+      <c r="A14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E13" s="12" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="2" t="s">
+      <c r="B14" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>17</v>
+      <c r="E14" s="11" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1634,95 +1637,112 @@
       <c r="B15" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>34</v>
+      <c r="C15" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="2"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="12"/>
+      <c r="D17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="11"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="12"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="11"/>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="11"/>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="12"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="11"/>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
-      <c r="E22" s="12"/>
+      <c r="E22" s="11"/>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
-      <c r="E23" s="12"/>
+      <c r="E23" s="11"/>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
-      <c r="E24" s="12"/>
+      <c r="E24" s="11"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
-      <c r="E25" s="12"/>
+      <c r="E25" s="11"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/JsonConverter/ExcelFiles/UI.xlsx
+++ b/JsonConverter/ExcelFiles/UI.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13776" windowHeight="8400"/>
+    <workbookView windowWidth="16524" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="50">
   <si>
     <t>아이디</t>
   </si>
@@ -131,6 +131,15 @@
     <t>StationMarket</t>
   </si>
   <si>
+    <t>UI_Popup_09</t>
+  </si>
+  <si>
+    <t>Scoreboard</t>
+  </si>
+  <si>
+    <t>Lobby</t>
+  </si>
+  <si>
     <t>UI_Panel_01</t>
   </si>
   <si>
@@ -147,9 +156,6 @@
   </si>
   <si>
     <t>GameLobby</t>
-  </si>
-  <si>
-    <t>Lobby</t>
   </si>
   <si>
     <t>UI_Panel_04</t>
@@ -1378,7 +1384,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="15.5555555555556" customWidth="1"/>
@@ -1584,16 +1590,16 @@
         <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="11" t="s">
         <v>36</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1601,50 +1607,50 @@
         <v>37</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="3" t="s">
+      <c r="C14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" customFormat="1" spans="1:6">
-      <c r="A14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="12" t="s">
+      <c r="E14" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+    </row>
+    <row r="15" customFormat="1" spans="1:6">
       <c r="A15" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="12" t="s">
         <v>42</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1654,39 +1660,49 @@
       <c r="B16" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>44</v>
+      <c r="C16" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E17" s="11" t="s">
+      <c r="D18" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="2"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="11"/>
+      <c r="E18" s="11" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2"/>
@@ -1711,9 +1727,9 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
       <c r="E22" s="11"/>
     </row>
     <row r="23" spans="1:5">
@@ -1744,6 +1760,13 @@
       <c r="D26" s="2"/>
       <c r="E26" s="11"/>
     </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="11"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/JsonConverter/ExcelFiles/UI.xlsx
+++ b/JsonConverter/ExcelFiles/UI.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="52">
   <si>
     <t>아이디</t>
   </si>
@@ -162,6 +162,12 @@
   </si>
   <si>
     <t>Upgrade</t>
+  </si>
+  <si>
+    <t>UI_Panel_05</t>
+  </si>
+  <si>
+    <t>Achievement</t>
   </si>
   <si>
     <t>UI_Loading_01</t>
@@ -1384,7 +1390,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="15.5555555555556" customWidth="1"/>
@@ -1677,39 +1683,49 @@
       <c r="B17" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>46</v>
+      <c r="C17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>36</v>
+      <c r="D18" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="E18" s="11" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="2"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="11"/>
+      <c r="A19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2"/>
@@ -1734,9 +1750,9 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
       <c r="E23" s="11"/>
     </row>
     <row r="24" spans="1:5">
@@ -1767,6 +1783,13 @@
       <c r="D27" s="2"/>
       <c r="E27" s="11"/>
     </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="11"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/JsonConverter/ExcelFiles/UI.xlsx
+++ b/JsonConverter/ExcelFiles/UI.xlsx
@@ -1724,7 +1724,7 @@
         <v>36</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:5">

--- a/JsonConverter/ExcelFiles/UI.xlsx
+++ b/JsonConverter/ExcelFiles/UI.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16524" windowHeight="8400"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="54">
   <si>
     <t>아이디</t>
   </si>
@@ -183,6 +183,12 @@
   </si>
   <si>
     <t>DebugUI</t>
+  </si>
+  <si>
+    <t>UI_Intro_01</t>
+  </si>
+  <si>
+    <t>Intro</t>
   </si>
 </sst>
 </file>
@@ -1728,11 +1734,19 @@
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="2"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
+      <c r="A20" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>49</v>
+      </c>
       <c r="D20" s="12"/>
-      <c r="E20" s="11"/>
+      <c r="E20" s="11" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2"/>

--- a/JsonConverter/ExcelFiles/UI.xlsx
+++ b/JsonConverter/ExcelFiles/UI.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="60">
   <si>
     <t>아이디</t>
   </si>
@@ -189,6 +189,24 @@
   </si>
   <si>
     <t>Intro</t>
+  </si>
+  <si>
+    <t>UI_Tutorial_01</t>
+  </si>
+  <si>
+    <t>TutorialOverlay</t>
+  </si>
+  <si>
+    <t>UI_Tutorial_02</t>
+  </si>
+  <si>
+    <t>HowToMove</t>
+  </si>
+  <si>
+    <t>UI_Tutorial_03</t>
+  </si>
+  <si>
+    <t>HowToLoop</t>
   </si>
 </sst>
 </file>
@@ -1749,25 +1767,49 @@
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="2"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
+      <c r="A21" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>49</v>
+      </c>
       <c r="D21" s="12"/>
-      <c r="E21" s="11"/>
+      <c r="E21" s="11" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="2"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
+      <c r="A22" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="D22" s="12"/>
-      <c r="E22" s="11"/>
+      <c r="E22" s="11" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="2"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
+      <c r="A23" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="D23" s="12"/>
-      <c r="E23" s="11"/>
+      <c r="E23" s="11" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2"/>

--- a/JsonConverter/ExcelFiles/UI.xlsx
+++ b/JsonConverter/ExcelFiles/UI.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="62">
   <si>
     <t>아이디</t>
   </si>
@@ -168,6 +168,12 @@
   </si>
   <si>
     <t>Achievement</t>
+  </si>
+  <si>
+    <t>UI_Panel_06</t>
+  </si>
+  <si>
+    <t>Currency</t>
   </si>
   <si>
     <t>UI_Loading_01</t>
@@ -1414,7 +1420,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="15.5555555555556" customWidth="1"/>
@@ -1724,44 +1730,44 @@
       <c r="B18" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>48</v>
-      </c>
+      <c r="C18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="3"/>
       <c r="E18" s="11" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>36</v>
+      <c r="D19" s="12" t="s">
+        <v>50</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" s="12"/>
+      <c r="C20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E20" s="11" t="s">
         <v>17</v>
       </c>
@@ -1773,8 +1779,8 @@
       <c r="B21" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>49</v>
+      <c r="C21" s="12" t="s">
+        <v>51</v>
       </c>
       <c r="D21" s="12"/>
       <c r="E21" s="11" t="s">
@@ -1788,8 +1794,8 @@
       <c r="B22" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>16</v>
+      <c r="C22" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="D22" s="12"/>
       <c r="E22" s="11" t="s">
@@ -1812,11 +1818,19 @@
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="11"/>
+      <c r="A24" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="12"/>
+      <c r="E24" s="11" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2"/>
@@ -1846,6 +1860,13 @@
       <c r="D28" s="2"/>
       <c r="E28" s="11"/>
     </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="11"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/JsonConverter/ExcelFiles/UI.xlsx
+++ b/JsonConverter/ExcelFiles/UI.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8400"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="66">
   <si>
     <t>아이디</t>
   </si>
@@ -140,6 +140,12 @@
     <t>Lobby</t>
   </si>
   <si>
+    <t>UI_Popup_10</t>
+  </si>
+  <si>
+    <t>Option</t>
+  </si>
+  <si>
     <t>UI_Panel_01</t>
   </si>
   <si>
@@ -174,6 +180,12 @@
   </si>
   <si>
     <t>Currency</t>
+  </si>
+  <si>
+    <t>UI_Panel_07</t>
+  </si>
+  <si>
+    <t>Setting</t>
   </si>
   <si>
     <t>UI_Loading_01</t>
@@ -1420,7 +1432,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="15.5555555555556" customWidth="1"/>
@@ -1643,67 +1655,67 @@
         <v>37</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="11" t="s">
-        <v>39</v>
+      <c r="E13" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="D14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="3" t="s">
+      <c r="C15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" customFormat="1" spans="1:6">
-      <c r="A15" s="2" t="s">
+      <c r="E15" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+    </row>
+    <row r="16" customFormat="1" spans="1:6">
       <c r="A16" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="12" t="s">
         <v>44</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>36</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1714,7 +1726,7 @@
         <v>46</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>36</v>
@@ -1731,11 +1743,13 @@
         <v>48</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D18" s="3"/>
+        <v>40</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="E18" s="11" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1745,59 +1759,59 @@
       <c r="B19" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>50</v>
-      </c>
+      <c r="C19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="3"/>
       <c r="E19" s="11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="C20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="3"/>
       <c r="E20" s="11" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="C21" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" s="12"/>
+      <c r="D21" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="E21" s="11" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="12"/>
+      <c r="C22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E22" s="11" t="s">
         <v>17</v>
       </c>
@@ -1809,8 +1823,8 @@
       <c r="B23" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>16</v>
+      <c r="C23" s="12" t="s">
+        <v>55</v>
       </c>
       <c r="D23" s="12"/>
       <c r="E23" s="11" t="s">
@@ -1824,8 +1838,8 @@
       <c r="B24" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>16</v>
+      <c r="C24" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="D24" s="12"/>
       <c r="E24" s="11" t="s">
@@ -1833,18 +1847,34 @@
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="11"/>
+      <c r="A25" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="12"/>
+      <c r="E25" s="11" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="11"/>
+      <c r="A26" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" s="12"/>
+      <c r="E26" s="11" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2"/>
@@ -1867,6 +1897,20 @@
       <c r="D29" s="2"/>
       <c r="E29" s="11"/>
     </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="11"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="11"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/JsonConverter/ExcelFiles/UI.xlsx
+++ b/JsonConverter/ExcelFiles/UI.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="68">
   <si>
     <t>아이디</t>
   </si>
@@ -144,6 +144,12 @@
   </si>
   <si>
     <t>Option</t>
+  </si>
+  <si>
+    <t>UI_Popup_11</t>
+  </si>
+  <si>
+    <t>Accomplished</t>
   </si>
   <si>
     <t>UI_Panel_01</t>
@@ -1432,7 +1438,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="15.5555555555556" customWidth="1"/>
@@ -1672,67 +1678,65 @@
         <v>39</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>41</v>
+        <v>16</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="D15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="3" t="s">
+      <c r="C16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" customFormat="1" spans="1:6">
-      <c r="A16" s="2" t="s">
+      <c r="E16" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+    </row>
+    <row r="17" customFormat="1" spans="1:5">
       <c r="A17" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="12" t="s">
         <v>46</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>36</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1743,7 +1747,7 @@
         <v>48</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>36</v>
@@ -1760,11 +1764,13 @@
         <v>50</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D19" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="E19" s="11" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1775,11 +1781,11 @@
         <v>52</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1789,44 +1795,44 @@
       <c r="B21" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>54</v>
-      </c>
+      <c r="C21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" s="3"/>
       <c r="E21" s="11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C22" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>36</v>
+      <c r="D22" s="12" t="s">
+        <v>56</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C23" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23" s="12"/>
+      <c r="C23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E23" s="11" t="s">
         <v>17</v>
       </c>
@@ -1838,8 +1844,8 @@
       <c r="B24" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>55</v>
+      <c r="C24" s="12" t="s">
+        <v>57</v>
       </c>
       <c r="D24" s="12"/>
       <c r="E24" s="11" t="s">
@@ -1853,8 +1859,8 @@
       <c r="B25" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>16</v>
+      <c r="C25" s="3" t="s">
+        <v>57</v>
       </c>
       <c r="D25" s="12"/>
       <c r="E25" s="11" t="s">
@@ -1877,11 +1883,19 @@
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="11"/>
+      <c r="A27" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="12"/>
+      <c r="E27" s="11" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2"/>
@@ -1911,6 +1925,13 @@
       <c r="D31" s="2"/>
       <c r="E31" s="11"/>
     </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="11"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/JsonConverter/ExcelFiles/UI.xlsx
+++ b/JsonConverter/ExcelFiles/UI.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="70">
   <si>
     <t>아이디</t>
   </si>
@@ -150,6 +150,12 @@
   </si>
   <si>
     <t>Accomplished</t>
+  </si>
+  <si>
+    <t>UI_Popup_12</t>
+  </si>
+  <si>
+    <t>ShipStat</t>
   </si>
   <si>
     <t>UI_Panel_01</t>
@@ -1438,7 +1444,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="15.5555555555556" customWidth="1"/>
@@ -1693,67 +1699,67 @@
         <v>41</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>43</v>
+        <v>23</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="D16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" s="3" t="s">
+      <c r="C17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" customFormat="1" spans="1:5">
-      <c r="A17" s="2" t="s">
+      <c r="E17" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+    </row>
+    <row r="18" customFormat="1" spans="1:5">
       <c r="A18" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="12" t="s">
         <v>48</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>36</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1764,7 +1770,7 @@
         <v>50</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>36</v>
@@ -1781,11 +1787,13 @@
         <v>52</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D20" s="3"/>
+        <v>44</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="E20" s="11" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1796,11 +1804,11 @@
         <v>54</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1810,44 +1818,44 @@
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>56</v>
-      </c>
+      <c r="C22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="3"/>
       <c r="E22" s="11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="C23" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>36</v>
+      <c r="D23" s="12" t="s">
+        <v>58</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="D24" s="12"/>
+      <c r="C24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E24" s="11" t="s">
         <v>17</v>
       </c>
@@ -1859,8 +1867,8 @@
       <c r="B25" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>57</v>
+      <c r="C25" s="12" t="s">
+        <v>59</v>
       </c>
       <c r="D25" s="12"/>
       <c r="E25" s="11" t="s">
@@ -1874,8 +1882,8 @@
       <c r="B26" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>16</v>
+      <c r="C26" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="D26" s="12"/>
       <c r="E26" s="11" t="s">
@@ -1898,11 +1906,19 @@
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="11"/>
+      <c r="A28" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D28" s="12"/>
+      <c r="E28" s="11" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2"/>
@@ -1932,6 +1948,13 @@
       <c r="D32" s="2"/>
       <c r="E32" s="11"/>
     </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="11"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/JsonConverter/ExcelFiles/UI.xlsx
+++ b/JsonConverter/ExcelFiles/UI.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="70">
   <si>
     <t>아이디</t>
   </si>
@@ -212,7 +212,7 @@
     <t>UI_Debug_01</t>
   </si>
   <si>
-    <t>DebugUI</t>
+    <t>DebugMenu</t>
   </si>
   <si>
     <t>UI_Intro_01</t>
@@ -1853,9 +1853,7 @@
       <c r="C24" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="D24" s="2"/>
       <c r="E24" s="11" t="s">
         <v>17</v>
       </c>
